--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260714.xlsx
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1,936</t>
+          <t>37,075,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>37,075,000</t>
+          <t>1,936</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
